--- a/docs/maklerhandbuch/06_Interessentenmanagement.xlsx
+++ b/docs/maklerhandbuch/06_Interessentenmanagement.xlsx
@@ -9,15 +9,19 @@
     <sheet sheetId="3" name="Feldbeschreibung" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Besichtigungen" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Angebote" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Controlling" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Absagegruende" state="visible" r:id="rId10"/>
+    <sheet sheetId="6" name="Funnel" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Preisindikatoren" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Preislogik" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Objektpipeline" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Controlling" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Absagegruende" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="478">
   <si>
     <t>06 · Interessentenmanagement – Objektkopf</t>
   </si>
@@ -484,6 +488,756 @@
     <t>offen</t>
   </si>
   <si>
+    <t>06 · Neunstufiger Käuferfunnel</t>
+  </si>
+  <si>
+    <t>Eine Stufe wird nur mit belegtem Kriterium gesetzt. Rückstufungen sind normal und werden dokumentiert. Ab Stufe 3 vollständiges Dossier, ab Stufe 7 Namensnennung gegenüber dem Eigentümer.</t>
+  </si>
+  <si>
+    <t>Bezeichnung</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>Übergangskriterium</t>
+  </si>
+  <si>
+    <t>Aktion</t>
+  </si>
+  <si>
+    <t>Pflichtdaten</t>
+  </si>
+  <si>
+    <t>Abbruchgrund</t>
+  </si>
+  <si>
+    <t>Lead</t>
+  </si>
+  <si>
+    <t>Kontakt ist bekannt, es liegt keine Äusserung zu diesem Objekt vor.</t>
+  </si>
+  <si>
+    <t>Kontaktdaten und Quelle erfasst.</t>
+  </si>
+  <si>
+    <t>Kurzdossier zustellen, Qualifizierungsgespräch anbieten.</t>
+  </si>
+  <si>
+    <t>Name, Kontakt, Quelle, Datum</t>
+  </si>
+  <si>
+    <t>Keine Reaktion nach zwei Kontaktversuchen.</t>
+  </si>
+  <si>
+    <t>Hat sich zu diesem Objekt gemeldet, Kaufabsicht unbestimmt.</t>
+  </si>
+  <si>
+    <t>Anfrage zu diesem Objekt liegt vor.</t>
+  </si>
+  <si>
+    <t>Qualifizierungsgespräch nach Käuferprofil führen.</t>
+  </si>
+  <si>
+    <t>Haushalt, Wohnsituation, Zeithorizont</t>
+  </si>
+  <si>
+    <t>Reine Wertneugier oder Marktbeobachtung.</t>
+  </si>
+  <si>
+    <t>Qualifizierter Interessent</t>
+  </si>
+  <si>
+    <t>Kaufabsicht ist plausibel, Finanzierung selbstdeklariert, erwerbsrechtlich zulässig.</t>
+  </si>
+  <si>
+    <t>Käuferprofil vollständig; Staatsangehörigkeit, Wohnsitz und Nutzungsabsicht erfasst; Eigenmittel plausibel (R34).</t>
+  </si>
+  <si>
+    <t>Vollständiges Dossier gegen Empfangsbestätigung; Besichtigung terminieren.</t>
+  </si>
+  <si>
+    <t>Finanzierungsstand, Eigenmittel, Bank, Nutzungsabsicht, Entscheidungsbefugnis</t>
+  </si>
+  <si>
+    <t>Erwerbsrechtlich unzulässig; Eigenmittel offensichtlich nicht ausreichend; kein Entscheidungsträger erreichbar.</t>
+  </si>
+  <si>
+    <t>Besichtigung</t>
+  </si>
+  <si>
+    <t>Hat das Objekt besichtigt.</t>
+  </si>
+  <si>
+    <t>Besichtigung durchgeführt und protokolliert; Offenlegung der Mängel vermerkt (R10).</t>
+  </si>
+  <si>
+    <t>Rückmeldung innerhalb von 48 Stunden strukturiert erheben.</t>
+  </si>
+  <si>
+    <t>Preisempfinden, Bedenken, nächster Schritt</t>
+  </si>
+  <si>
+    <t>Absage mit erfasstem Grund.</t>
+  </si>
+  <si>
+    <t>Qualifizierter Käufer</t>
+  </si>
+  <si>
+    <t>Verfolgt den Kauf weiter und hat die Finanzierung in Abklärung oder bestätigt.</t>
+  </si>
+  <si>
+    <t>Zweitbesichtigung oder ausdrückliche Kaufabsicht mit Terminvorstellung; Finanzierungsabklärung nachweislich eingeleitet.</t>
+  </si>
+  <si>
+    <t>Angebotsformular abgeben und erläutern; objektbezogene Bankbestätigung verlangen.</t>
+  </si>
+  <si>
+    <t>Kaufpreisrahmen, gewünschter Übergabetermin, Bedingungen</t>
+  </si>
+  <si>
+    <t>Finanzierungsabklärung wird nicht eingeleitet.</t>
+  </si>
+  <si>
+    <t>Hat ein schriftliches Angebot eingereicht.</t>
+  </si>
+  <si>
+    <t>Angebot schriftlich, unterzeichnet, mit Eingangsvermerk (Datum und Uhrzeit).</t>
+  </si>
+  <si>
+    <t>Vollständigkeit prüfen, fehlende Angaben mit Frist nachfordern.</t>
+  </si>
+  <si>
+    <t>Angebotspreis, Bedingungen, Vorbehalte, Gültigkeit</t>
+  </si>
+  <si>
+    <t>Angebot wird zurückgezogen oder läuft ab.</t>
+  </si>
+  <si>
+    <t>Verhandlungsfähiges Angebot</t>
+  </si>
+  <si>
+    <t>Angebot ist vollständig und finanziell belegt.</t>
+  </si>
+  <si>
+    <t>Gate 6 ist passiert: objektbezogene Finanzierungsbestätigung, Eigenmittelnachweis mit hartem Anteil, erwerbsrechtliche Zulässigkeit geklärt, GwG-Triage abgeschlossen (R37, R40).</t>
+  </si>
+  <si>
+    <t>In den Angebotsvergleich aufnehmen; Entscheidungsvorlage für den Eigentümer.</t>
+  </si>
+  <si>
+    <t>Finanzierungsbestätigung, Abschlusswahrscheinlichkeit, Nettoerlös</t>
+  </si>
+  <si>
+    <t>Finanzierungsbestätigung wird nicht beigebracht; Bewilligung wird verweigert.</t>
+  </si>
+  <si>
+    <t>Vertragskandidat</t>
+  </si>
+  <si>
+    <t>Einigung erzielt, Reservation ausgestellt, Notariat beauftragt.</t>
+  </si>
+  <si>
+    <t>Gate 8 ist passiert; Reservationsbestätigung unterzeichnet; Identifikation abgeschlossen.</t>
+  </si>
+  <si>
+    <t>Notariat begleiten; Zweitinteressenten in Wartestellung halten.</t>
+  </si>
+  <si>
+    <t>Beurkundungstermin, offene Bedingungen</t>
+  </si>
+  <si>
+    <t>Rücktritt vor Beurkundung – bis dahin sind beide Seiten frei (R1, R2).</t>
+  </si>
+  <si>
+    <t>Käufer</t>
+  </si>
+  <si>
+    <t>Kaufvertrag ist beurkundet.</t>
+  </si>
+  <si>
+    <t>Öffentliche Beurkundung erfolgt (R1). Eigentümer wird die Person erst mit dem Grundbucheintrag (R3).</t>
+  </si>
+  <si>
+    <t>Vollzug und Übergabe begleiten.</t>
+  </si>
+  <si>
+    <t>Zahlungs- und Eintragungsstand, Übergabetermin</t>
+  </si>
+  <si>
+    <t>Rückabwicklung – nur über Notariat und Rechtsberatung.</t>
+  </si>
+  <si>
+    <t>06 · Marktindikatoren für die Preissteuerung</t>
+  </si>
+  <si>
+    <t>Kein Indikator wird allein interpretiert. Eine Preisreduktion ist nie die erste Massnahme und niemals eine Folge des Zeitablaufs. Entscheidungslogiken P1 bis P8 im Blatt Preislogik.</t>
+  </si>
+  <si>
+    <t>Indikator</t>
+  </si>
+  <si>
+    <t>Erhebung</t>
+  </si>
+  <si>
+    <t>Aussage</t>
+  </si>
+  <si>
+    <t>Woche 1</t>
+  </si>
+  <si>
+    <t>Woche 2</t>
+  </si>
+  <si>
+    <t>Woche 3</t>
+  </si>
+  <si>
+    <t>Woche 4</t>
+  </si>
+  <si>
+    <t>Kumuliert</t>
+  </si>
+  <si>
+    <t>Auslösekriterium erreicht</t>
+  </si>
+  <si>
+    <t>Anzahl Anfragen</t>
+  </si>
+  <si>
+    <t>CRM, je Kalenderwoche und kumuliert</t>
+  </si>
+  <si>
+    <t>Reichweite und Preisakzeptanz auf der ersten Stufe</t>
+  </si>
+  <si>
+    <t>nein</t>
+  </si>
+  <si>
+    <t>Qualität der Anfragen</t>
+  </si>
+  <si>
+    <t>Anteil Anfragen, die die Qualifizierung erreichen</t>
+  </si>
+  <si>
+    <t>Trifft das Inserat die Zielgruppe?</t>
+  </si>
+  <si>
+    <t>Quote Anfrage zu Besichtigung</t>
+  </si>
+  <si>
+    <t>Besichtigungen geteilt durch Anfragen</t>
+  </si>
+  <si>
+    <t>Stimmen Inseratsversprechen und Objekt überein?</t>
+  </si>
+  <si>
+    <t>Anzahl Besichtigungen</t>
+  </si>
+  <si>
+    <t>Besichtigungsjournal</t>
+  </si>
+  <si>
+    <t>Tatsächliches Interesse</t>
+  </si>
+  <si>
+    <t>Anzahl qualifizierte Besichtigungen</t>
+  </si>
+  <si>
+    <t>Besichtigungen mit Funnelstufe 3 oder höher</t>
+  </si>
+  <si>
+    <t>Substanz der Nachfrage</t>
+  </si>
+  <si>
+    <t>Anzahl Zweitbesichtigungen</t>
+  </si>
+  <si>
+    <t>Besichtigungsjournal, Feld Art</t>
+  </si>
+  <si>
+    <t>Stärkster Frühindikator für ein Angebot</t>
+  </si>
+  <si>
+    <t>Quote Besichtigung zu Angebot</t>
+  </si>
+  <si>
+    <t>Angebote geteilt durch Besichtigungen</t>
+  </si>
+  <si>
+    <t>Preisakzeptanz nach Objektkenntnis</t>
+  </si>
+  <si>
+    <t>Anzahl Angebote</t>
+  </si>
+  <si>
+    <t>Angebotsjournal</t>
+  </si>
+  <si>
+    <t>Marktergebnis</t>
+  </si>
+  <si>
+    <t>Angebotshöhe und Abstand zum Angebotspreis</t>
+  </si>
+  <si>
+    <t>Angebotsjournal, Feld Abweichung</t>
+  </si>
+  <si>
+    <t>Höhe der Preiskorrektur, die der Markt vornimmt</t>
+  </si>
+  <si>
+    <t>Finanzierungssicherheit der Angebote</t>
+  </si>
+  <si>
+    <t>Anteil mit objektbezogener Bankbestätigung</t>
+  </si>
+  <si>
+    <t>Belastbarkeit der Angebote</t>
+  </si>
+  <si>
+    <t>Absagegründe</t>
+  </si>
+  <si>
+    <t>CRM, Verteilung nach Grund</t>
+  </si>
+  <si>
+    <t>Ursache der Nichtakzeptanz – der wichtigste Indikator</t>
+  </si>
+  <si>
+    <t>Konkurrenzangebote im Segment</t>
+  </si>
+  <si>
+    <t>Marktbeobachtung, monatlich</t>
+  </si>
+  <si>
+    <t>Angebotsdruck</t>
+  </si>
+  <si>
+    <t>Preisänderungen der Konkurrenz</t>
+  </si>
+  <si>
+    <t>Marktrichtung im Segment</t>
+  </si>
+  <si>
+    <t>Tage am Markt</t>
+  </si>
+  <si>
+    <t>Ab Starttag, automatisch</t>
+  </si>
+  <si>
+    <t>Nur im Verhältnis zur segmentüblichen Dauer aussagekräftig, nie allein</t>
+  </si>
+  <si>
+    <t>06 · Entscheidungslogik Preissteuerung P1 bis P8</t>
+  </si>
+  <si>
+    <t>Vor jeder Preisempfehlung die zutreffende Logik bestimmen und die Ursachenanalyse dokumentieren (Kontrollpunkt K3).</t>
+  </si>
+  <si>
+    <t>Situation</t>
+  </si>
+  <si>
+    <t>WENN</t>
+  </si>
+  <si>
+    <t>Interpretation</t>
+  </si>
+  <si>
+    <t>DANN</t>
+  </si>
+  <si>
+    <t>SONST</t>
+  </si>
+  <si>
+    <t>NIE</t>
+  </si>
+  <si>
+    <t>Trifft zu</t>
+  </si>
+  <si>
+    <t>Massnahme und Datum</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>Wenige Anfragen, kaum Besichtigungen – über die gesamte erste Marktphase</t>
+  </si>
+  <si>
+    <t>Anfragen liegen deutlich unter dem, was vergleichbare Objekte im Segment auslösen, und die Quote Anfrage zu Besichtigung ist unauffällig.</t>
+  </si>
+  <si>
+    <t>Das Objekt wird in der Trefferliste nicht geöffnet. Ursache liegt vor der Besichtigung: Preispositionierung, Leitbild, Titel, Suchfilter oder Kanal.</t>
+  </si>
+  <si>
+    <t>Zuerst Darstellung und Auffindbarkeit prüfen: Leitbild und Bildreihenfolge, Titel, Pflichtfelder und Suchfilter der Portale, Zimmerzahl und Flächenangaben, Kanalauswahl. Änderungen umsetzen und eine weitere Marktphase messen.</t>
+  </si>
+  <si>
+    <t>Bleibt der Effekt nach der Korrektur aus, liegt die Ursache in der Preispositionierung. Dann Preisgespräch mit dokumentierter Analyse und Handlungsmöglichkeiten.</t>
+  </si>
+  <si>
+    <t>Keine Preisreduktion, solange Darstellung und Auffindbarkeit nicht geprüft sind. Eine Reduktion bei schlechtem Leitbild wirkt nicht und ist verloren.</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>Viele Anfragen, aber kaum Besichtigungen</t>
+  </si>
+  <si>
+    <t>Anfragen sind zahlreich, die Quote Anfrage zu Besichtigung ist tief.</t>
+  </si>
+  <si>
+    <t>Das Inserat verspricht etwas anderes als das Objekt, oder die Unterlagen klären etwas, das abschreckt: Lage, Zustand, Sanierungsbedarf, Dienstbarkeit, Preis im Verhältnis zur Fläche.</t>
+  </si>
+  <si>
+    <t>Absagegründe der Anfragenden strukturiert erheben. Häufigsten Grund gezielt adressieren: Angabe korrigieren, Sachverhalt im Inserat früher benennen, Zielgruppe anpassen.</t>
+  </si>
+  <si>
+    <t>Zeigt sich als Hauptgrund durchgehend der Preis im Verhältnis zum Gebotenen, ist die Positionierung zu überprüfen.</t>
+  </si>
+  <si>
+    <t>Keine Beschönigung der Unterlagen, um die Quote zu heben. Das verlagert den Abbruch nur auf die Besichtigung und beschädigt die Glaubwürdigkeit.</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Ausreichend Besichtigungen, keine Angebote</t>
+  </si>
+  <si>
+    <t>Zehn oder mehr Besichtigungen ohne Angebot, keine Zweitbesichtigungen.</t>
+  </si>
+  <si>
+    <t>Das Objekt überzeugt in der Besichtigung nicht zum verlangten Preis. Ursache ist Zustand, Grundriss, Umfeld oder Preis-Leistungs-Empfinden.</t>
+  </si>
+  <si>
+    <t>Absagegründe auswerten. Bei überwiegend objektbezogenen Gründen: gezielte Massnahmen prüfen – Zustandsanalyse beilegen, Sanierungsbedarf beziffern, Teilmassnahme ausführen, Inventar einbeziehen. Bei überwiegend preisbezogenen Gründen: Preisgespräch.</t>
+  </si>
+  <si>
+    <t>Lehnt der Eigentümer sowohl Massnahme als auch Preisanpassung ab, ist das Ergebnis zu protokollieren und die Erwartung schriftlich anzupassen.</t>
+  </si>
+  <si>
+    <t>Keine Sammelbesichtigungen, um Aktivität zu zeigen. Das erzeugt Zahlen ohne Substanz.</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>Angebote kommen, aber deutlich unter dem Angebotspreis</t>
+  </si>
+  <si>
+    <t>Mehrere unabhängige Angebote liegen in einem engen Band deutlich unter dem Angebotspreis.</t>
+  </si>
+  <si>
+    <t>Der Markt hat einen Preis gebildet. Mehrere unabhängige Angebote im gleichen Band sind die belastbarste Preisinformation, die überhaupt zu erhalten ist – belastbarer als jede Bewertung.</t>
+  </si>
+  <si>
+    <t>Dem Eigentümer das Band, die Finanzierungssicherheit und den Nettoerlös je Angebot vorlegen. Prüfen, ob das Band innerhalb der bewerteten Spanne liegt.</t>
+  </si>
+  <si>
+    <t>Liegt das Band unter der Spanne, ist die Bewertung gegen die tatsächliche Marktreaktion zu prüfen und die Abweichung zu erklären, nicht zu verteidigen.</t>
+  </si>
+  <si>
+    <t>Angebote nicht vorenthalten, weil sie zu tief erscheinen. Jedes Angebot wird vorgelegt.</t>
+  </si>
+  <si>
+    <t>P5</t>
+  </si>
+  <si>
+    <t>Mehrere Angebote gleichzeitig, teilweise über dem Angebotspreis</t>
+  </si>
+  <si>
+    <t>Zwei oder mehr verhandlungsfähige Angebote innerhalb kurzer Zeit.</t>
+  </si>
+  <si>
+    <t>Der Angebotspreis lag unter der Absetzbarkeit, oder die Nachfrage im Segment ist angespannt.</t>
+  </si>
+  <si>
+    <t>Transparentes Verfahren mit gleicher Information und gleicher Frist für alle festlegen, vom Eigentümer beschliessen lassen und schriftlich kommunizieren. Nicht nur den Preis vergleichen, sondern die Abschlusssicherheit.</t>
+  </si>
+  <si>
+    <t>Ist der Eigentümer versucht, nachträglich den Angebotspreis zu erhöhen: Konsequenzen benennen – Vertrauensverlust, Abbruchrisiko bei allen Bietenden, Reputationsschaden. Entscheid dokumentieren.</t>
+  </si>
+  <si>
+    <t>Keine Auktionsmechanik ohne vorherige Offenlegung gegenüber allen Beteiligten. Keine Weitergabe konkurrierender Angebotsbeträge.</t>
+  </si>
+  <si>
+    <t>P6</t>
+  </si>
+  <si>
+    <t>Ein Angebot, aber mit unsicherer Finanzierung</t>
+  </si>
+  <si>
+    <t>Angebot liegt preislich im Zielbereich, die Finanzierung ist nur selbstdeklariert oder mit Vorbehalt bestätigt.</t>
+  </si>
+  <si>
+    <t>Ein Angebot ohne belegte Finanzierung ist kein Angebot, sondern eine Absicht. Das Hauptrisiko ist nicht der Preis, sondern der Zeitverlust bei einem Abbruch.</t>
+  </si>
+  <si>
+    <t>Objektbezogene Bankbestätigung mit Frist verlangen. Vermarktung bis dahin nicht zurückstellen und Zweitinteressenten nicht absagen.</t>
+  </si>
+  <si>
+    <t>Wird die Bestätigung nicht beigebracht, wird das Angebot nicht weiterverfolgt; Gate 6 ist nicht passiert.</t>
+  </si>
+  <si>
+    <t>Keine Reservation und keine Rückstellung der Vermarktung auf eine Selbstauskunft hin.</t>
+  </si>
+  <si>
+    <t>P7</t>
+  </si>
+  <si>
+    <t>Nachfrage bricht nach einer Preisreduktion nicht an</t>
+  </si>
+  <si>
+    <t>Nach einer umgesetzten Reduktion bleiben Anfragen und Besichtigungen auf dem Vorniveau.</t>
+  </si>
+  <si>
+    <t>Der Preis war nicht die bindende Ursache, oder die Reduktion war zu klein, um eine andere Suchfilterstufe zu erreichen.</t>
+  </si>
+  <si>
+    <t>Keine zweite Reduktion in kurzem Abstand. Ursachenanalyse wiederholen und die Filterlogik der Portale prüfen: eine Reduktion, die keine Preisstufe überschreitet, wird von der Zielgruppe nicht gesehen.</t>
+  </si>
+  <si>
+    <t>Grundsatzgespräch mit dem Eigentümer: Rückzug vom Markt mit Neuaufstellung nach Wartezeit oder Fortsetzung mit angepasster Erwartung.</t>
+  </si>
+  <si>
+    <t>Keine Reduktionskette in kurzen Abständen. Sie signalisiert Not und zerstört die Verhandlungsposition endgültig.</t>
+  </si>
+  <si>
+    <t>P8</t>
+  </si>
+  <si>
+    <t>Marktumfeld verändert sich während der Vermarktung</t>
+  </si>
+  <si>
+    <t>Zinsniveau, Angebotsdruck im Segment oder Konkurrenzpreise verändern sich deutlich.</t>
+  </si>
+  <si>
+    <t>Die Grundlage der Preisstrategie hat sich geändert, unabhängig vom Objekt.</t>
+  </si>
+  <si>
+    <t>Marktanalyse aktualisieren und dem Eigentümer als eigenen Punkt vorlegen – getrennt von objektbezogenen Ursachen.</t>
+  </si>
+  <si>
+    <t>Bei Verschlechterung und fehlender Anpassungsbereitschaft: Erwartung zur Vermarktungsdauer schriftlich anpassen.</t>
+  </si>
+  <si>
+    <t>Marktveränderung nicht als Begründung für eine Reduktion verwenden, ohne sie mit Zahlen zu belegen.</t>
+  </si>
+  <si>
+    <t>06 · Objektstatus im CRM</t>
+  </si>
+  <si>
+    <t>Genau ein Status ist aktuell. Bei «Verloren» ist der Verlustgrund zu erfassen.</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Bedeutung</t>
+  </si>
+  <si>
+    <t>Pflichtfelder</t>
+  </si>
+  <si>
+    <t>Aktuell</t>
+  </si>
+  <si>
+    <t>Seit</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Verkaufsanlass erkannt, Eigentümer noch nicht kontaktiert</t>
+  </si>
+  <si>
+    <t>Quelle, Objektadresse, nächste Aktion</t>
+  </si>
+  <si>
+    <t>Erstkontakt</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Kontakt aufgenommen, Qualifizierung läuft</t>
+  </si>
+  <si>
+    <t>Qualifizierungsergebnis, Termin</t>
+  </si>
+  <si>
+    <t>Eigentümergespräch</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Erstgespräch geführt, Bewertungsauftrag erteilt</t>
+  </si>
+  <si>
+    <t>Erstgesprächsprotokoll, Verfügungsbefugnis</t>
+  </si>
+  <si>
+    <t>Bewertung</t>
+  </si>
+  <si>
+    <t>4–9</t>
+  </si>
+  <si>
+    <t>Aufnahme, Unterlagen, Rechtsprüfung, Bewertung, Preisentscheid</t>
+  </si>
+  <si>
+    <t>Gate 1 und Gate 3 Stand, Preisentscheid</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Mandat unterzeichnet, Onboarding abgeschlossen</t>
+  </si>
+  <si>
+    <t>Gate 2 Stand, Triage-Ergebnis, Budget</t>
+  </si>
+  <si>
+    <t>Vorbereitung</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Vermarktungsmittel in Erstellung</t>
+  </si>
+  <si>
+    <t>Release-Checkliste, Eigentümerfreigabe</t>
+  </si>
+  <si>
+    <t>Vermarktungsfreigabe</t>
+  </si>
+  <si>
+    <t>Gate 4 und Gate 5 in Prüfung</t>
+  </si>
+  <si>
+    <t>Gate-Protokolle, Starttag</t>
+  </si>
+  <si>
+    <t>Aktiv am Markt</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Veröffentlicht, Anfragen laufen</t>
+  </si>
+  <si>
+    <t>Starttag, Indikatoren, Wochenreport</t>
+  </si>
+  <si>
+    <t>Besichtigungen</t>
+  </si>
+  <si>
+    <t>13–14</t>
+  </si>
+  <si>
+    <t>Qualifizierung und Besichtigungen laufen</t>
+  </si>
+  <si>
+    <t>Funnelverteilung, Absagegründe</t>
+  </si>
+  <si>
+    <t>Angebote</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Mindestens ein Angebot eingegangen</t>
+  </si>
+  <si>
+    <t>Angebotsjournal, Gate 6 Stand</t>
+  </si>
+  <si>
+    <t>Verhandlung</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Verhandlungsauftrag erteilt, Runden laufen</t>
+  </si>
+  <si>
+    <t>Verhandlungsauftrag, Protokoll, Gate 7</t>
+  </si>
+  <si>
+    <t>Notariat</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Reservation ausgestellt, Notariat beauftragt</t>
+  </si>
+  <si>
+    <t>Gate 8 Stand, Beurkundungstermin</t>
+  </si>
+  <si>
+    <t>Beurkundet</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Kaufvertrag öffentlich beurkundet</t>
+  </si>
+  <si>
+    <t>Gate 9 Stand, Fristenplan</t>
+  </si>
+  <si>
+    <t>Vollzug</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Zahlung und Grundbucheintragung laufen</t>
+  </si>
+  <si>
+    <t>Zahlungs- und Eintragungsstand</t>
+  </si>
+  <si>
+    <t>Übergabe</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Eintragung bestätigt, Übergabe terminiert</t>
+  </si>
+  <si>
+    <t>Gate 10 Stand, Übergabetermin</t>
+  </si>
+  <si>
+    <t>Abgeschlossen</t>
+  </si>
+  <si>
+    <t>Übergeben, abgerechnet, archiviert</t>
+  </si>
+  <si>
+    <t>Abschlusscheckliste, Archivvermerk, Wiedervorlage</t>
+  </si>
+  <si>
+    <t>Verloren</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Mandat nicht erteilt, gekündigt oder Objekt zurückgezogen</t>
+  </si>
+  <si>
+    <t>Verlustgrund, Zeitpunkt, Wiedervorlage</t>
+  </si>
+  <si>
     <t>06 · Controlling-Dashboard</t>
   </si>
   <si>
@@ -496,24 +1250,15 @@
     <t>Wert</t>
   </si>
   <si>
-    <t>Definition</t>
-  </si>
-  <si>
     <t>Orientierung und Handlungsauslöser</t>
   </si>
   <si>
-    <t>Tage am Markt</t>
-  </si>
-  <si>
     <t>Kalendertage seit der Veröffentlichung</t>
   </si>
   <si>
     <t>Segmentabhängig; ab 90 Tagen Strategieüberprüfung</t>
   </si>
   <si>
-    <t>Anzahl Anfragen</t>
-  </si>
-  <si>
     <t>Alle eingegangenen Kontaktaufnahmen</t>
   </si>
   <si>
@@ -544,9 +1289,6 @@
     <t>Im CRM erfasste Personen oder Haushalte</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
     <t>Anzahl qualifizierte Interessenten</t>
   </si>
   <si>
@@ -556,30 +1298,24 @@
     <t>Mindestens 20 Prozent der Anfragen</t>
   </si>
   <si>
-    <t>Anzahl Besichtigungen</t>
+    <t>Anzahl verhandlungsfähige Interessenten</t>
+  </si>
+  <si>
+    <t>Funnelstufe 7 und höher: Angebot vollständig und finanziell belegt</t>
+  </si>
+  <si>
+    <t>Der Indikator, der Abschlussnähe tatsächlich abbildet</t>
   </si>
   <si>
     <t>Durchgeführte Termine</t>
   </si>
   <si>
-    <t>Quote Anfrage zu Besichtigung</t>
-  </si>
-  <si>
-    <t>Besichtigungen geteilt durch Anfragen</t>
-  </si>
-  <si>
     <t>Tiefe Quote deutet auf Preis- oder Erwartungsproblem</t>
   </si>
   <si>
-    <t>Anzahl Zweitbesichtigungen</t>
-  </si>
-  <si>
     <t>Termine mit demselben Interessenten</t>
   </si>
   <si>
-    <t>Stärkster Frühindikator für ein Angebot</t>
-  </si>
-  <si>
     <t>Anzahl Absagen</t>
   </si>
   <si>
@@ -595,9 +1331,6 @@
     <t>Häufung bei «Preis» ab 5 Nennungen erfordert Preisgespräch</t>
   </si>
   <si>
-    <t>Anzahl Angebote</t>
-  </si>
-  <si>
     <t>Schriftlich eingegangene Kaufangebote</t>
   </si>
   <si>
@@ -641,12 +1374,6 @@
   </si>
   <si>
     <t>Möglichst keine; jede Reduktion schwächt die Verhandlungsposition</t>
-  </si>
-  <si>
-    <t>Quote Besichtigung zu Angebot</t>
-  </si>
-  <si>
-    <t>Angebote geteilt durch Besichtigungen</t>
   </si>
   <si>
     <t>Unter 10 Prozent nach 10 Besichtigungen: Ursache klären</t>
@@ -1510,6 +2237,513 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="4" width="56" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B4" s="6">
+        <f>IF(Objekt!$B$26="","",TODAY()-Objekt!$B$26)</f>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="B8" s="6">
+        <f>COUNTA(Interessenten!C4:C400)</f>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="B9" s="6">
+        <f>COUNTIF(Interessenten!T4:T400,"3 Qualifizierter Interessent")+COUNTIF(Interessenten!T4:T400,"4 Besichtigung")+COUNTIF(Interessenten!T4:T400,"5 Qualifizierter Käufer")+COUNTIF(Interessenten!T4:T400,"6 Angebot")+COUNTIF(Interessenten!T4:T400,"7 Verhandlungsfähiges Angebot")+COUNTIF(Interessenten!T4:T400,"8 Vertragskandidat")+COUNTIF(Interessenten!T4:T400,"9 Käufer")</f>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="B10" s="6">
+        <f>COUNTIF(Interessenten!T4:T400,"7 Verhandlungsfähiges Angebot")+COUNTIF(Interessenten!T4:T400,"8 Vertragskandidat")+COUNTIF(Interessenten!T4:T400,"9 Käufer")</f>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="B11" s="6">
+        <f>COUNTA(Besichtigungen!D4:D200)</f>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B12" s="6">
+        <f>IF(COUNTA(Interessenten!C4:C400)=0,"",COUNTA(Besichtigungen!D4:D200)/COUNTA(Interessenten!C4:C400))</f>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B13" s="6">
+        <f>COUNTIF(Besichtigungen!G4:G200,"Zweitbesichtigung")</f>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="B14" s="6">
+        <f>COUNTIF(Interessenten!AA4:AA400,"abgesagt")</f>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B16" s="6">
+        <f>COUNT(Angebote!E4:E200)</f>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="B18" s="6">
+        <f>IF(COUNT(Angebote!G4:G200)=0,"",AVERAGE(Angebote!G4:G200))</f>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="B19" s="6">
+        <f>IF(COUNT(Angebote!G4:G200)=0,"",MAX(Angebote!G4:G200))</f>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B20" s="6">
+        <f>IF(OR(COUNT(Angebote!G4:G200)=0,Objekt!$B$22=""),"",MAX(Angebote!G4:G200)/Objekt!$B$22-1)</f>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="B23" s="6">
+        <f>IF(COUNTA(Besichtigungen!D4:D200)=0,"",COUNT(Angebote!E4:E200)/COUNTA(Besichtigungen!D4:D200))</f>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="C27" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>462</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:D3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="B4" s="5">
+        <f>COUNTIF(Interessenten!AB4:AB400,A4)</f>
+      </c>
+      <c r="C4" s="6"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="B5" s="7">
+        <f>COUNTIF(Interessenten!AB4:AB400,A5)</f>
+      </c>
+      <c r="C5" s="6"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B6" s="5">
+        <f>COUNTIF(Interessenten!AB4:AB400,A6)</f>
+      </c>
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="B7" s="7">
+        <f>COUNTIF(Interessenten!AB4:AB400,A7)</f>
+      </c>
+      <c r="C7" s="6"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="B8" s="5">
+        <f>COUNTIF(Interessenten!AB4:AB400,A8)</f>
+      </c>
+      <c r="C8" s="6"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="B9" s="7">
+        <f>COUNTIF(Interessenten!AB4:AB400,A9)</f>
+      </c>
+      <c r="C9" s="6"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="B10" s="5">
+        <f>COUNTIF(Interessenten!AB4:AB400,A10)</f>
+      </c>
+      <c r="C10" s="6"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="B11" s="7">
+        <f>COUNTIF(Interessenten!AB4:AB400,A11)</f>
+      </c>
+      <c r="C11" s="6"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="B12" s="5">
+        <f>COUNTIF(Interessenten!AB4:AB400,A12)</f>
+      </c>
+      <c r="C12" s="6"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="B13" s="7">
+        <f>COUNTIF(Interessenten!AB4:AB400,A13)</f>
+      </c>
+      <c r="C13" s="6"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:C3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
@@ -3875,13 +5109,13 @@
       <formula1>"hoch,mittel,gering,keines"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="T10:T63">
-      <formula1>"A,B,C"</formula1>
+      <formula1>"1 Lead,2 Interessent,3 Qualifizierter Interessent,4 Besichtigung,5 Qualifizierter Käufer,6 Angebot,7 Verhandlungsfähiges Angebot,8 Vertragskandidat,9 Käufer"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="T4:T63">
-      <formula1>"A,B,C"</formula1>
+      <formula1>"1 Lead,2 Interessent,3 Qualifizierter Interessent,4 Besichtigung,5 Qualifizierter Käufer,6 Angebot,7 Verhandlungsfähiges Angebot,8 Vertragskandidat,9 Käufer"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="T4:T263">
-      <formula1>"A,B,C"</formula1>
+      <formula1>"1 Lead,2 Interessent,3 Qualifizierter Interessent,4 Besichtigung,5 Qualifizierter Käufer,6 Angebot,7 Verhandlungsfähiges Angebot,8 Vertragskandidat,9 Käufer"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="U10:U63">
       <formula1>"nein,angekündigt,eingegangen,zurückgezogen"</formula1>
@@ -5808,352 +7042,277 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="4" width="56" customWidth="1"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="5" max="6" width="44" customWidth="1"/>
+    <col min="7" max="7" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>155</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-    </row>
-    <row r="2" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>156</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="F3" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B4" s="6">
-        <f>IF(Objekt!$B$26="","",TODAY()-Objekt!$B$26)</f>
+      <c r="G3" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>163</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B5" s="6"/>
+        <v>165</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
+        <v>2</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>130</v>
+      </c>
       <c r="C5" s="7" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B6" s="6"/>
+        <v>170</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>3</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>174</v>
+      </c>
       <c r="C6" s="5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="B7" s="6"/>
+        <v>176</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>4</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>180</v>
+      </c>
       <c r="C7" s="7" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B8" s="6">
-        <f>COUNTA(Interessenten!C4:C400)</f>
+        <v>182</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>5</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>186</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="B9" s="6">
-        <f>COUNTIF(Interessenten!T4:T400,"A")</f>
+        <v>188</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>6</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B10" s="6">
-        <f>COUNTA(Besichtigungen!D4:D200)</f>
+        <v>193</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>7</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>197</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B11" s="6">
-        <f>IF(COUNTA(Interessenten!C4:C400)=0,"",COUNTA(Besichtigungen!D4:D200)/COUNTA(Interessenten!C4:C400))</f>
+        <v>199</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>203</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="B12" s="6">
-        <f>COUNTIF(Besichtigungen!G4:G200,"Zweitbesichtigung")</f>
+        <v>205</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>9</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="B13" s="6">
-        <f>COUNTIF(Interessenten!AA4:AA400,"abgesagt")</f>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="B15" s="6">
-        <f>COUNT(Angebote!E4:E200)</f>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="B17" s="6">
-        <f>IF(COUNT(Angebote!G4:G200)=0,"",AVERAGE(Angebote!G4:G200))</f>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="B18" s="6">
-        <f>IF(COUNT(Angebote!G4:G200)=0,"",MAX(Angebote!G4:G200))</f>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B19" s="6">
-        <f>IF(OR(COUNT(Angebote!G4:G200)=0,Objekt!$B$22=""),"",MAX(Angebote!G4:G200)/Objekt!$B$22-1)</f>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="B22" s="6">
-        <f>IF(COUNTA(Besichtigungen!D4:D200)=0,"",COUNT(Angebote!E4:E200)/COUNTA(Besichtigungen!D4:D200))</f>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="7" t="s">
+      <c r="E12" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="F12" s="5" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>221</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:D3"/>
+  <autoFilter ref="A3:G3"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -6162,135 +7321,1050 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="70" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="56" customWidth="1"/>
+    <col min="4" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>224</v>
       </c>
+      <c r="I3" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:I3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" sqref="I10:I17">
+      <formula1>"ja,nein,offen"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="I4:I17">
+      <formula1>"ja,nein,offen"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="I4:I217">
+      <formula1>"ja,nein,offen"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="4" max="4" width="56" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="7" width="50" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="B3" s="3" t="s">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B4" s="5">
-        <f>COUNTIF(Interessenten!AB4:AB400,A4)</f>
-      </c>
-      <c r="C4" s="6"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="B5" s="7">
-        <f>COUNTIF(Interessenten!AB4:AB400,A5)</f>
-      </c>
-      <c r="C5" s="6"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="B6" s="5">
-        <f>COUNTIF(Interessenten!AB4:AB400,A6)</f>
-      </c>
-      <c r="C6" s="6"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="I6" s="6"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="B7" s="7">
-        <f>COUNTIF(Interessenten!AB4:AB400,A7)</f>
-      </c>
-      <c r="C7" s="6"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="B8" s="5">
-        <f>COUNTIF(Interessenten!AB4:AB400,A8)</f>
-      </c>
-      <c r="C8" s="6"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="B9" s="7">
-        <f>COUNTIF(Interessenten!AB4:AB400,A9)</f>
-      </c>
-      <c r="C9" s="6"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="B10" s="5">
-        <f>COUNTIF(Interessenten!AB4:AB400,A10)</f>
-      </c>
-      <c r="C10" s="6"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="B11" s="7">
-        <f>COUNTIF(Interessenten!AB4:AB400,A11)</f>
-      </c>
-      <c r="C11" s="6"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="I11" s="6"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:I3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" sqref="H10:H11">
+      <formula1>"ja,nein,offen"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H4:H11">
+      <formula1>"ja,nein,offen"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H4:H211">
+      <formula1>"ja,nein,offen"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="56" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B12" s="5">
-        <f>COUNTIF(Interessenten!AB4:AB400,A12)</f>
-      </c>
-      <c r="C12" s="6"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="B13" s="7">
-        <f>COUNTIF(Interessenten!AB4:AB400,A13)</f>
-      </c>
-      <c r="C13" s="6"/>
+        <v>374</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F20" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:C3"/>
+  <autoFilter ref="A3:F3"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" sqref="E10:E20">
+      <formula1>"ja,nein,offen"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E4:E20">
+      <formula1>"ja,nein,offen"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E4:E220">
+      <formula1>"ja,nein,offen"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
